--- a/esyluban/examples/dev/DataTables/test/composite_tables.xlsx
+++ b/esyluban/examples/dev/DataTables/test/composite_tables.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="test.TbCompositeJsonTable3" &amp; value_type="test.CompositeJsonTable3" &amp; mode="one" &amp; read_schema_from_file="false" &amp; input="table3@test/composite_tables.json" &amp; output="test_tbcompositejsontable3"</t>
+          <t>full_name="test.TbCompositeJsonTable3" &amp; mode="one" &amp; input="table3@test/composite_tables.json"</t>
         </is>
       </c>
     </row>
@@ -459,23 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
